--- a/data/trans_dic/P32B-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P32B-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha sentido mal o culpable por su forma de beber</t>
+          <t>Población que se ha sentido mal o culpable por su forma de beber (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 5,27</t>
+          <t>0,64; 5,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,12; 16,09</t>
+          <t>6,63; 16,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 12,25</t>
+          <t>3,97; 12,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 8,52</t>
+          <t>0,87; 9,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,77</t>
+          <t>0,0; 8,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,82</t>
+          <t>0,0; 6,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 9,84</t>
+          <t>1,68; 9,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,08</t>
+          <t>0,87; 5,14</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,1; 10,64</t>
+          <t>4,53; 10,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,85; 10,44</t>
+          <t>3,79; 9,99</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,04</t>
+          <t>0,59; 5,61</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,86</t>
+          <t>0,43; 4,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 6,24</t>
+          <t>1,3; 6,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,38</t>
+          <t>0,0; 6,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,14</t>
+          <t>0,3; 2,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,88</t>
+          <t>0,91; 4,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>0,0; 4,15</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 8,53</t>
+          <t>1,97; 7,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,95</t>
+          <t>0,0; 4,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,93</t>
+          <t>0,49; 5,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,33</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,07</t>
+          <t>1,8; 5,94</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,1</t>
+          <t>0,41; 3,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,45</t>
+          <t>0,0; 3,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,53</t>
+          <t>0,0; 4,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,66</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,91</t>
+          <t>0,39; 3,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,24</t>
+          <t>0,17; 1,99</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,66</t>
+          <t>0,0; 4,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 8,93</t>
+          <t>1,5; 9,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 9,3</t>
+          <t>1,02; 9,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,67</t>
+          <t>0,0; 23,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,65</t>
+          <t>0,0; 4,23</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,94</t>
+          <t>1,09; 6,81</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,77</t>
+          <t>0,7; 6,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,13</t>
+          <t>0,0; 6,27</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,59</t>
+          <t>0,0; 5,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,03</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,07</t>
+          <t>0,52; 5,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,02</t>
+          <t>0,8; 5,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,19</t>
+          <t>0,85; 7,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 5,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 6,04</t>
+          <t>0,57; 6,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,91</t>
+          <t>0,62; 4,03</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,36</t>
+          <t>0,65; 3,7</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,39</t>
+          <t>1,02; 4,13</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,56</t>
+          <t>1,99; 6,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,09</t>
+          <t>1,69; 5,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,35</t>
+          <t>0,99; 4,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,01</t>
+          <t>0,44; 3,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,29</t>
+          <t>0,8; 4,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 4,66</t>
+          <t>0,16; 4,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,99</t>
+          <t>1,8; 4,9</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,7</t>
+          <t>1,66; 4,46</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,64</t>
+          <t>0,71; 3,67</t>
         </is>
       </c>
     </row>
@@ -1702,57 +1702,57 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,52</t>
+          <t>0,91; 3,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,81</t>
+          <t>0,41; 2,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,65</t>
+          <t>0,24; 2,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,4</t>
+          <t>0,38; 3,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,7</t>
+          <t>0,0; 4,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,3</t>
+          <t>0,24; 1,49</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,69</t>
+          <t>0,79; 2,68</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,89</t>
+          <t>0,27; 1,84</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,43</t>
+          <t>0,41; 2,42</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,32</t>
+          <t>0,49; 1,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,65</t>
+          <t>2,17; 3,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,86</t>
+          <t>1,51; 2,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,92</t>
+          <t>1,35; 3,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,82</t>
+          <t>0,51; 2,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,38</t>
+          <t>0,3; 1,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,68</t>
+          <t>0,57; 1,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,4</t>
+          <t>0,58; 2,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,28</t>
+          <t>0,59; 1,32</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,73</t>
+          <t>1,61; 2,68</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,26</t>
+          <t>1,3; 2,2</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,35</t>
+          <t>1,13; 2,37</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha sentido mal o culpable por su forma de beber</t>
+          <t>Población que se ha sentido mal o culpable por su forma de beber (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>63; 7709</t>
+          <t>934; 8454</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10739; 28209</t>
+          <t>11616; 28588</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7307; 21885</t>
+          <t>7099; 21633</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1492; 15319</t>
+          <t>1573; 16356</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 7912</t>
+          <t>0; 6540</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 7486</t>
+          <t>0; 7347</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1799; 10443</t>
+          <t>1787; 10277</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 694</t>
+          <t>0; 889</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1933; 11160</t>
+          <t>1905; 11295</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11678; 30323</t>
+          <t>12915; 30697</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10963; 29726</t>
+          <t>10794; 28465</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1608; 16331</t>
+          <t>1594; 15183</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>931; 8835</t>
+          <t>991; 9417</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3915; 19348</t>
+          <t>4022; 19594</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2007</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 18770</t>
+          <t>0; 16022</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1909</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2073</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2000</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1526</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1009; 9482</t>
+          <t>900; 8716</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3850; 17907</t>
+          <t>4181; 19784</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2012</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 16047</t>
+          <t>0; 15418</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1948</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1895</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4988</t>
+          <t>0; 5174</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4042; 15795</t>
+          <t>3641; 14611</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1872</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4925</t>
+          <t>0; 5041</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1850</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>438; 4446</t>
+          <t>446; 4887</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1932</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 5563</t>
+          <t>0; 4958</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4352</t>
+          <t>0; 4016</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5109; 16731</t>
+          <t>4953; 16367</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>972; 9765</t>
+          <t>964; 9003</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4339</t>
+          <t>0; 4706</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 8027</t>
+          <t>0; 7066</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4965</t>
+          <t>0; 4980</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5931</t>
+          <t>0; 5981</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 1992</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2064</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3306</t>
+          <t>0; 3021</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1172; 10748</t>
+          <t>1455; 11656</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 4739</t>
+          <t>0; 4677</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 6812</t>
+          <t>0; 8170</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>761; 6755</t>
+          <t>506; 5994</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4511</t>
+          <t>0; 4301</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1929; 11446</t>
+          <t>1925; 12152</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>905; 8480</t>
+          <t>928; 8648</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1267</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2009</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1990</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 1746</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2375</t>
+          <t>0; 2046</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5266</t>
+          <t>0; 6095</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1876; 10822</t>
+          <t>1995; 12417</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>963; 8709</t>
+          <t>905; 8958</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2437</t>
+          <t>0; 2490</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 8915</t>
+          <t>0; 10214</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5577</t>
+          <t>0; 5760</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>951; 9581</t>
+          <t>980; 9494</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1405; 8287</t>
+          <t>1324; 8674</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>947; 8040</t>
+          <t>949; 8060</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1962</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3838</t>
+          <t>0; 5605</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>526; 5825</t>
+          <t>552; 6135</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1815; 11976</t>
+          <t>1906; 12337</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5307</t>
+          <t>0; 5349</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1815; 9907</t>
+          <t>1903; 10896</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2813; 11478</t>
+          <t>2655; 10800</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1960</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8294; 26074</t>
+          <t>7912; 25798</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6525; 23246</t>
+          <t>6465; 22125</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3035; 13409</t>
+          <t>3051; 13141</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 1923</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>941; 8555</t>
+          <t>936; 8321</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2061; 13417</t>
+          <t>2018; 12321</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>538; 18610</t>
+          <t>629; 18343</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 1954</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10491; 30464</t>
+          <t>10980; 29930</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10985; 29885</t>
+          <t>10568; 28335</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4956; 25782</t>
+          <t>5009; 25957</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 5890</t>
+          <t>0; 5930</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4221; 15965</t>
+          <t>4114; 16595</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1855; 12841</t>
+          <t>1850; 12328</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>648; 7338</t>
+          <t>659; 7910</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>931; 8153</t>
+          <t>918; 7945</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 5438</t>
+          <t>0; 5957</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 2078</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 5648</t>
+          <t>0; 4344</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1657; 9551</t>
+          <t>1757; 10903</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4928; 17949</t>
+          <t>5251; 17919</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1852; 13617</t>
+          <t>1938; 13253</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1409; 9126</t>
+          <t>1527; 9072</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>8534; 24749</t>
+          <t>9219; 24710</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>43502; 74590</t>
+          <t>44262; 77238</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>30624; 57266</t>
+          <t>30208; 58754</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>20826; 46118</t>
+          <t>21348; 48429</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4061; 16261</t>
+          <t>4583; 18108</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3043; 14437</t>
+          <t>3117; 14522</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5964; 19275</t>
+          <t>6479; 19812</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>6984; 24659</t>
+          <t>5925; 23663</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>15956; 35383</t>
+          <t>16469; 36675</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>50990; 84477</t>
+          <t>49859; 82695</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>39831; 71195</t>
+          <t>40930; 69369</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>29953; 61236</t>
+          <t>29293; 61773</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32B-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P32B-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,78</t>
+          <t>0,62; 5,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,63; 16,31</t>
+          <t>6,34; 15,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 12,11</t>
+          <t>3,83; 12,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 9,09</t>
+          <t>0,72; 6,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,9</t>
+          <t>0,0; 9,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,7</t>
+          <t>0,0; 6,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 9,68</t>
+          <t>1,66; 9,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 3,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,14</t>
+          <t>0,87; 5,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,53; 10,77</t>
+          <t>4,46; 10,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 9,99</t>
+          <t>3,96; 10,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,61</t>
+          <t>0,47; 4,54</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,12</t>
+          <t>0,39; 3,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,32</t>
+          <t>1,27; 5,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,3</t>
+          <t>0,0; 5,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,89</t>
+          <t>0,33; 3,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,29</t>
+          <t>0,84; 4,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,15</t>
+          <t>0,0; 3,83</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 7,89</t>
+          <t>2,72; 9,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,41</t>
+          <t>0,47; 4,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,94</t>
+          <t>2,45; 7,04</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -1137,27 +1137,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,78</t>
+          <t>0,41; 3,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,0; 2,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,57</t>
+          <t>0,0; 4,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1172,27 +1172,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,16</t>
+          <t>0,4; 3,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,12</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,99</t>
+          <t>0,26; 1,89</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,44</t>
+          <t>0,0; 4,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 9,48</t>
+          <t>1,51; 8,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 9,49</t>
+          <t>0,97; 9,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,83</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,23</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 6,81</t>
+          <t>1,1; 6,58</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,96</t>
+          <t>0,72; 7,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,27</t>
+          <t>0,0; 5,49</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -1417,27 +1417,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,26</t>
+          <t>0,0; 5,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,13</t>
+          <t>0,0; 2,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,02</t>
+          <t>0,53; 5,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,26</t>
+          <t>0,66; 4,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,21</t>
+          <t>0,72; 7,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,31</t>
+          <t>0,0; 4,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,36</t>
+          <t>0,56; 6,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,03</t>
+          <t>0,62; 4,26</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,7</t>
+          <t>0,64; 3,6</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,13</t>
+          <t>1,03; 4,36</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -1562,17 +1562,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,49</t>
+          <t>2,04; 6,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,79</t>
+          <t>1,69; 5,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,27</t>
+          <t>1,67; 6,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,17 +1582,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,9</t>
+          <t>0,44; 4,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,86</t>
+          <t>0,84; 5,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 4,59</t>
+          <t>1,66; 8,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1602,17 +1602,17 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,9</t>
+          <t>1,75; 4,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,46</t>
+          <t>1,8; 4,68</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,67</t>
+          <t>2,22; 5,84</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -1697,32 +1697,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,66</t>
+          <t>0,9; 3,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,7</t>
+          <t>0,42; 3,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,86</t>
+          <t>0,23; 2,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,31</t>
+          <t>0,39; 3,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,78</t>
+          <t>0,0; 2,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1732,27 +1732,27 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,38</t>
+          <t>0,0; 4,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,49</t>
+          <t>0,23; 1,37</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,68</t>
+          <t>0,76; 2,65</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,84</t>
+          <t>0,27; 1,71</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,42</t>
+          <t>0,36; 2,36</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,31</t>
+          <t>0,45; 1,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,78</t>
+          <t>2,06; 3,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,93</t>
+          <t>1,56; 2,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,07</t>
+          <t>1,5; 3,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,02</t>
+          <t>0,55; 1,97</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,38</t>
+          <t>0,3; 1,41</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,73</t>
+          <t>0,54; 1,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,31</t>
+          <t>1,12; 3,32</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,32</t>
+          <t>0,6; 1,31</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,68</t>
+          <t>1,62; 2,73</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,2</t>
+          <t>1,3; 2,21</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,37</t>
+          <t>1,55; 2,87</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>498</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>4699</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>934; 8454</t>
+          <t>910; 7722</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11616; 28588</t>
+          <t>11122; 27729</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7099; 21633</t>
+          <t>6846; 23047</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1573; 16356</t>
+          <t>1228; 10817</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6540</t>
+          <t>0; 6680</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 7347</t>
+          <t>0; 7375</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1787; 10277</t>
+          <t>1760; 10179</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 889</t>
+          <t>0; 3021</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1905; 11295</t>
+          <t>1907; 11368</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12915; 30697</t>
+          <t>12719; 30043</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10794; 28465</t>
+          <t>11273; 28848</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1594; 15183</t>
+          <t>1262; 12118</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>2920</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>991; 9417</t>
+          <t>896; 8925</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4022; 19594</t>
+          <t>3945; 17918</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 16022</t>
+          <t>0; 14497</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>900; 8716</t>
+          <t>1000; 9331</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4181; 19784</t>
+          <t>3857; 18482</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 15418</t>
+          <t>0; 14620</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>9832</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9536</t>
+          <t>11545</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2635,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5174</t>
+          <t>0; 4763</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3641; 14611</t>
+          <t>5092; 17197</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5041</t>
+          <t>0; 5019</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>446; 4887</t>
+          <t>419; 4401</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2670,17 +2670,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4958</t>
+          <t>0; 4848</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4016</t>
+          <t>0; 4298</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4953; 16367</t>
+          <t>6774; 19465</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>979</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>2551</t>
         </is>
       </c>
     </row>
@@ -2833,27 +2833,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>964; 9003</t>
+          <t>966; 9460</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4706</t>
+          <t>0; 4600</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 7066</t>
+          <t>0; 7086</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4980</t>
+          <t>0; 5776</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5981</t>
+          <t>0; 5870</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2868,27 +2868,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3021</t>
+          <t>0; 3633</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1455; 11656</t>
+          <t>1459; 11865</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 4677</t>
+          <t>0; 5268</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 8170</t>
+          <t>0; 8576</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>506; 5994</t>
+          <t>884; 6460</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
     </row>
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4301</t>
+          <t>0; 4113</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1925; 12152</t>
+          <t>1942; 11328</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>928; 8648</t>
+          <t>885; 8522</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3076,27 +3076,27 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2046</t>
+          <t>0; 2560</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 6095</t>
+          <t>0; 4459</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1995; 12417</t>
+          <t>1999; 11995</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>905; 8958</t>
+          <t>927; 9137</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2490</t>
+          <t>0; 2472</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5721</t>
         </is>
       </c>
     </row>
@@ -3249,27 +3249,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 10214</t>
+          <t>0; 9873</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5760</t>
+          <t>0; 5322</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>980; 9494</t>
+          <t>998; 9788</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1324; 8674</t>
+          <t>1071; 7687</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>949; 8060</t>
+          <t>810; 7974</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3279,32 +3279,32 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5605</t>
+          <t>0; 4476</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>552; 6135</t>
+          <t>546; 6213</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1906; 12337</t>
+          <t>1906; 13028</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5349</t>
+          <t>0; 5328</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1903; 10896</t>
+          <t>1872; 10615</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2655; 10800</t>
+          <t>2678; 11386</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>9693</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>13232</t>
+          <t>21207</t>
         </is>
       </c>
     </row>
@@ -3462,17 +3462,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7912; 25798</t>
+          <t>8092; 25218</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6465; 22125</t>
+          <t>6448; 22841</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3051; 13141</t>
+          <t>5855; 23291</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3482,17 +3482,17 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>936; 8321</t>
+          <t>946; 9212</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2018; 12321</t>
+          <t>2132; 13318</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>629; 18343</t>
+          <t>3871; 20202</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3502,17 +3502,17 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10980; 29930</t>
+          <t>10680; 30394</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10568; 28335</t>
+          <t>11453; 29729</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5009; 25957</t>
+          <t>12941; 34051</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4399</t>
         </is>
       </c>
     </row>
@@ -3665,32 +3665,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 5930</t>
+          <t>0; 5101</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4114; 16595</t>
+          <t>4081; 15981</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1850; 12328</t>
+          <t>1916; 14300</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>659; 7910</t>
+          <t>735; 7819</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>918; 7945</t>
+          <t>929; 8093</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 5957</t>
+          <t>0; 4990</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3700,27 +3700,27 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4344</t>
+          <t>0; 5396</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1757; 10903</t>
+          <t>1687; 10062</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5251; 17919</t>
+          <t>5096; 17661</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1938; 13253</t>
+          <t>1939; 12348</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1527; 9072</t>
+          <t>1520; 10067</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30947</t>
+          <t>36366</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>13525</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>44472</t>
+          <t>53510</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>9219; 24710</t>
+          <t>8433; 24419</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>44262; 77238</t>
+          <t>42163; 75862</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>30208; 58754</t>
+          <t>31229; 57730</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21348; 48429</t>
+          <t>25195; 53349</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4583; 18108</t>
+          <t>4926; 17607</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3117; 14522</t>
+          <t>3102; 14773</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6479; 19812</t>
+          <t>6212; 20315</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5925; 23663</t>
+          <t>10156; 29995</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>16469; 36675</t>
+          <t>16605; 36431</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>49859; 82695</t>
+          <t>50203; 84351</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>40930; 69369</t>
+          <t>40959; 69605</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>29293; 61773</t>
+          <t>40166; 74234</t>
         </is>
       </c>
     </row>
